--- a/supplementary/Supplementary_Dataset_S2.xlsx
+++ b/supplementary/Supplementary_Dataset_S2.xlsx
@@ -426,77 +426,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>summary_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>depth_percent</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n_samples</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>n_observations</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mean_flagstat_mapped</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mean_idxstats_mapped</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean_mapped_diff</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_mapped_diff_pct</t>
+          <t>exact_concordance_count</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>sd_mapped_diff_pct</t>
+          <t>exact_concordance_pct</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>min_mapped_diff_pct</t>
+          <t>max_absolute_discrepancy</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>max_mapped_diff_pct</t>
+          <t>max_percentage_discrepancy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>10</v>
       </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
       <c r="C2" t="n">
-        <v>9291613</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>9291613</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>9291613</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -506,26 +508,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>20</v>
       </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
       <c r="C3" t="n">
-        <v>18585336.66666667</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>18585336.66666667</v>
+        <v>18585336.67</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>18585336.67</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -535,26 +539,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>30</v>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="n">
-        <v>27878534.66666667</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>27878534.66666667</v>
+        <v>27878534.67</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>27878534.67</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -564,26 +570,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>40</v>
       </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
       <c r="C5" t="n">
-        <v>37174918</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>37174918</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>37174918</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -593,26 +601,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>50</v>
       </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
       <c r="C6" t="n">
-        <v>46469421.33333334</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>46469421.33333334</v>
+        <v>46469421.33</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>46469421.33</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -622,26 +632,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>60</v>
       </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
       <c r="C7" t="n">
-        <v>55763827.66666666</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>55763827.66666666</v>
+        <v>55763827.67</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>55763827.67</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -651,26 +663,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>70</v>
       </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
       <c r="C8" t="n">
-        <v>65057337.33333334</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>65057337.33333334</v>
+        <v>65057337.33</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>65057337.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -680,26 +694,28 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>80</v>
       </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
       <c r="C9" t="n">
-        <v>74350424</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>74350424</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>74350424</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -709,31 +725,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>90</v>
       </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
       <c r="C10" t="n">
-        <v>83645806.33333333</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>83645806.33333333</v>
+        <v>83645806.33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>83645806.33</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46468579.89</v>
+      </c>
+      <c r="E11" t="n">
+        <v>46468579.89</v>
+      </c>
+      <c r="F11" t="n">
+        <v>27</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -748,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,46 +813,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Experiment</t>
+          <t>Study component</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Experiment 2a</t>
+          <t>Baseline concordance experiment</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Manuscript title</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>experiment-2a-reproducibility</t>
+          <t>A Reproducible Computational Benchmarking Framework for Evaluating Concordance Between BAM-Derived Mapped-Read Counts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Supplementary dataset accompanying the manuscript</t>
+          <t>experiment-2a-reproducibility</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Depth-level and overall summaries of mapped-read concordance for the baseline experiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Generated from</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>discrepancy_summary.tsv</t>
         </is>
